--- a/lab-standards/Asia-TTC-lab-standard.xlsx
+++ b/lab-standards/Asia-TTC-lab-standard.xlsx
@@ -560,6 +560,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -573,6 +577,10 @@
 Workshop/ lab – 1000 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -642,7 +650,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -664,7 +674,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -686,7 +698,9 @@
       <c r="C18" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -708,7 +722,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -730,7 +746,9 @@
       <c r="C20" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -752,7 +770,9 @@
       <c r="C21" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -774,7 +794,9 @@
       <c r="C22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -796,7 +818,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -818,7 +842,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -840,7 +866,9 @@
       <c r="C25" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -862,7 +890,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -884,7 +914,9 @@
       <c r="C27" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>7</v>
       </c>
@@ -906,7 +938,9 @@
       <c r="C28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -928,7 +962,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -950,7 +986,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>5</v>
       </c>
@@ -972,7 +1010,9 @@
       <c r="C31" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -994,7 +1034,9 @@
       <c r="C32" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>4</v>
       </c>
@@ -1016,7 +1058,9 @@
       <c r="C33" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>4</v>
       </c>
@@ -1162,6 +1206,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1175,6 +1223,10 @@
 Workshop/ lab – 600 sft</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1244,7 +1296,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1266,7 +1320,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1288,7 +1344,9 @@
       <c r="C18" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -1310,7 +1368,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -1332,7 +1392,9 @@
       <c r="C20" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -1354,7 +1416,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>7</v>
       </c>
@@ -1376,7 +1440,9 @@
       <c r="C22" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>4</v>
       </c>
@@ -1398,7 +1464,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>7</v>
       </c>
@@ -1420,7 +1488,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -1442,7 +1512,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -1464,7 +1536,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -1486,7 +1560,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>6</v>
       </c>
@@ -1508,7 +1584,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -1530,7 +1608,9 @@
       <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>7</v>
       </c>
@@ -1552,7 +1632,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>5</v>
       </c>
@@ -1574,7 +1656,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>5</v>
       </c>
@@ -1596,7 +1680,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>5</v>
       </c>
@@ -1618,7 +1704,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>
@@ -1640,7 +1728,9 @@
       <c r="C34" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>6</v>
       </c>
@@ -1662,7 +1752,9 @@
       <c r="C35" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -1808,6 +1900,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -1822,6 +1918,10 @@
 Classroom cum workshop-1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1891,7 +1991,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -1913,7 +2015,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -1935,7 +2039,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -1957,7 +2063,9 @@
       <c r="C19" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -1979,7 +2087,9 @@
       <c r="C20" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>8</v>
       </c>
@@ -2001,7 +2111,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -2023,7 +2135,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>9</v>
       </c>
@@ -2045,7 +2159,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>8</v>
       </c>
@@ -2067,7 +2183,9 @@
       <c r="C24" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>6</v>
       </c>
@@ -2089,7 +2207,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -2111,7 +2231,9 @@
       <c r="C26" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>6</v>
       </c>
@@ -2133,7 +2255,9 @@
       <c r="C27" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>5</v>
       </c>
@@ -2155,7 +2279,9 @@
       <c r="C28" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>5</v>
       </c>
@@ -2177,7 +2303,9 @@
       <c r="C29" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>4</v>
       </c>
@@ -2199,7 +2327,9 @@
       <c r="C30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>7</v>
       </c>
@@ -2221,7 +2351,9 @@
       <c r="C31" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>3</v>
       </c>
@@ -2367,6 +2499,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -2382,6 +2518,10 @@
 Classroom cum workshop – 1000 sft (93 sqm)</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2451,7 +2591,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -2473,7 +2615,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -2495,7 +2639,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>4</v>
       </c>
@@ -2517,7 +2663,9 @@
       <c r="C19" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>9</v>
       </c>
@@ -2539,7 +2687,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -2561,7 +2711,9 @@
       <c r="C21" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -2583,7 +2735,9 @@
       <c r="C22" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -2605,7 +2759,9 @@
       <c r="C23" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -2627,7 +2783,9 @@
       <c r="C24" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>4</v>
       </c>
@@ -2649,7 +2807,9 @@
       <c r="C25" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -2671,7 +2831,9 @@
       <c r="C26" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>4</v>
       </c>
@@ -2693,7 +2855,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -2715,7 +2879,9 @@
       <c r="C28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>8</v>
       </c>
@@ -2737,7 +2903,9 @@
       <c r="C29" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>3</v>
       </c>
@@ -2759,7 +2927,9 @@
       <c r="C30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>5</v>
       </c>
@@ -2781,7 +2951,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -2803,7 +2975,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -2825,7 +2999,9 @@
       <c r="C33" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
@@ -2847,7 +3023,9 @@
       <c r="C34" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -2869,7 +3047,9 @@
       <c r="C35" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>7</v>
       </c>
@@ -3015,6 +3195,10 @@
           <t>SICIP required space for 20 trainees</t>
         </is>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="12" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
@@ -3030,6 +3214,10 @@
 Classroom cum workshop – 1000 sft (93 sqm) Space for Plumbing booth not included</t>
         </is>
       </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3099,7 +3287,9 @@
       <c r="C16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -3121,7 +3311,9 @@
       <c r="C17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -3143,7 +3335,9 @@
       <c r="C18" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>9</v>
       </c>
@@ -3165,7 +3359,9 @@
       <c r="C19" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>6</v>
       </c>
@@ -3187,7 +3383,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>6</v>
       </c>
@@ -3209,7 +3407,9 @@
       <c r="C21" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>6</v>
       </c>
@@ -3231,7 +3431,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>6</v>
       </c>
@@ -3253,7 +3455,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>5</v>
       </c>
@@ -3275,7 +3479,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -3297,7 +3503,9 @@
       <c r="C25" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>5</v>
       </c>
@@ -3319,7 +3527,9 @@
       <c r="C26" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>5</v>
       </c>
@@ -3341,7 +3551,9 @@
       <c r="C27" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>4</v>
       </c>
@@ -3363,7 +3575,9 @@
       <c r="C28" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>7</v>
       </c>
@@ -3385,7 +3599,9 @@
       <c r="C29" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>8</v>
       </c>
@@ -3407,7 +3623,9 @@
       <c r="C30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>8</v>
       </c>
@@ -3429,7 +3647,9 @@
       <c r="C31" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>6</v>
       </c>
@@ -3451,7 +3671,9 @@
       <c r="C32" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -3473,7 +3695,9 @@
       <c r="C33" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>4</v>
       </c>
@@ -3495,7 +3719,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>6</v>
       </c>
@@ -3517,7 +3743,9 @@
       <c r="C35" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>8</v>
       </c>
@@ -3539,7 +3767,9 @@
       <c r="C36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>7</v>
       </c>
@@ -3561,7 +3791,9 @@
       <c r="C37" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>4</v>
       </c>
@@ -3583,7 +3815,9 @@
       <c r="C38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>5</v>
       </c>
@@ -3605,7 +3839,9 @@
       <c r="C39" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>3</v>
       </c>
@@ -3627,7 +3863,9 @@
       <c r="C40" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>3</v>
       </c>
@@ -3649,7 +3887,9 @@
       <c r="C41" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>3</v>
       </c>
@@ -3721,8 +3961,8 @@
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A43:E43"/>
     <mergeCell ref="A45:E45"/>
     <mergeCell ref="C8:G8"/>
   </mergeCells>
